--- a/iot-selenium/target/test-classes/testdata/frontend-testing.xlsx
+++ b/iot-selenium/target/test-classes/testdata/frontend-testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yamen\Downloads\iot-frontend\iot-selenium\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6280B1AD-4E19-4F86-889E-44E4FD862BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8278B81D-4316-4494-B64D-017751BB2B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Legend" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4004" uniqueCount="1330">
   <si>
     <t>Sensorix — Test Sheet Legend</t>
   </si>
@@ -3725,9 +3725,6 @@
     <t>Traffic table visible</t>
   </si>
   <si>
-    <t>Columns: Location Timestamp Density Avg Speed Congestion Vehicles/min</t>
-  </si>
-  <si>
     <t>Filter panel visible</t>
   </si>
   <si>
@@ -3866,9 +3863,6 @@
     <t>NoSuchElement — data-testid attribute missing from Air Quality card DOM element</t>
   </si>
   <si>
-    <t>Failed</t>
-  </si>
-  <si>
     <t>NoSuchElement — data-testid attribute missing from Street Lights card DOM element</t>
   </si>
   <si>
@@ -4017,6 +4011,645 @@
   </si>
   <si>
     <t>manual</t>
+  </si>
+  <si>
+    <t>TC-F13-01</t>
+  </si>
+  <si>
+    <t>Air Quality nav card is visible on /home</t>
+  </si>
+  <si>
+    <t>Air Quality nav card is visible</t>
+  </si>
+  <si>
+    <t>TC-F13-02</t>
+  </si>
+  <si>
+    <t>Clicking air quality card navigates to /air-quality-dashboard</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Click air quality nav card</t>
+  </si>
+  <si>
+    <t>URL contains /air-quality-dashboard</t>
+  </si>
+  <si>
+    <t>/air-quality-dashboard</t>
+  </si>
+  <si>
+    <t>TC-F13-03</t>
+  </si>
+  <si>
+    <t>Air Quality card has correct title text</t>
+  </si>
+  <si>
+    <t>Card text contains air quality or pollution keywords</t>
+  </si>
+  <si>
+    <t>TC-F13-04</t>
+  </si>
+  <si>
+    <t>TC-F13-05</t>
+  </si>
+  <si>
+    <t>Authenticated user opens /air-quality-dashboard, page root visible</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Navigate to /air-quality-dashboard</t>
+  </si>
+  <si>
+    <t>TC-F13-06</t>
+  </si>
+  <si>
+    <t>TC-F13-07</t>
+  </si>
+  <si>
+    <t>Air quality readings table visible</t>
+  </si>
+  <si>
+    <t>TC-F13-08</t>
+  </si>
+  <si>
+    <t>Columns: Location, Timestamp, CO, Ozone, NO2, SO2, PM2.5, PM10, Pollution</t>
+  </si>
+  <si>
+    <t>TC-F13-09</t>
+  </si>
+  <si>
+    <t>TC-F13-10</t>
+  </si>
+  <si>
+    <t>TC-F13-11</t>
+  </si>
+  <si>
+    <t>TC-F13-12</t>
+  </si>
+  <si>
+    <t>1. Seed sensors. 2. Open /air-quality-dashboard. 3. Read first row text.</t>
+  </si>
+  <si>
+    <t>First row text contains one of: CAIRO_NASR_CITY, CAIRO_MAADI, CAIRO_HELIOPOLIS</t>
+  </si>
+  <si>
+    <t>Verifies row contains real data</t>
+  </si>
+  <si>
+    <t>TC-F13-13</t>
+  </si>
+  <si>
+    <t>Unauthenticated user redirected to /login from /air-quality-dashboard</t>
+  </si>
+  <si>
+    <t>1. No login. 2. Navigate to /air-quality-dashboard</t>
+  </si>
+  <si>
+    <t>TC-F14-01</t>
+  </si>
+  <si>
+    <t>Filter by CAIRO_NASR_CITY location</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select Nasr City. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_NASR_CITY;expected_location=CAIRO_NASR_CITY</t>
+  </si>
+  <si>
+    <t>Only CAIRO_NASR_CITY rows shown</t>
+  </si>
+  <si>
+    <t>TC-F14-02</t>
+  </si>
+  <si>
+    <t>Filter by CAIRO_MAADI location</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select Maadi. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_MAADI;expected_location=CAIRO_MAADI</t>
+  </si>
+  <si>
+    <t>Only CAIRO_MAADI rows shown</t>
+  </si>
+  <si>
+    <t>TC-F14-03</t>
+  </si>
+  <si>
+    <t>Filter by CAIRO_HELIOPOLIS location</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select Heliopolis. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_HELIOPOLIS;expected_location=CAIRO_HELIOPOLIS</t>
+  </si>
+  <si>
+    <t>Only CAIRO_HELIOPOLIS rows shown</t>
+  </si>
+  <si>
+    <t>TC-F14-04</t>
+  </si>
+  <si>
+    <t>Filter by GOOD pollution level</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select GOOD. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;pollutionLevel=GOOD;expected_pollution=GOOD</t>
+  </si>
+  <si>
+    <t>Only GOOD pollution rows shown</t>
+  </si>
+  <si>
+    <t>TC-F14-05</t>
+  </si>
+  <si>
+    <t>Filter by MODERATE pollution level</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;pollutionLevel=MODERATE;expected_pollution=MODERATE</t>
+  </si>
+  <si>
+    <t>Only MODERATE pollution rows shown</t>
+  </si>
+  <si>
+    <t>TC-F14-06</t>
+  </si>
+  <si>
+    <t>Filter by UNHEALTHY pollution level</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select UNHEALTHY. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;pollutionLevel=UNHEALTHY;expected_pollution=UNHEALTHY</t>
+  </si>
+  <si>
+    <t>Only UNHEALTHY pollution rows shown</t>
+  </si>
+  <si>
+    <t>TC-F14-07</t>
+  </si>
+  <si>
+    <t>Filter by VERY_UNHEALTHY pollution level</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select VERY_UNHEALTHY. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;pollutionLevel=VERY_UNHEALTHY;expected_pollution=VERY_UNHEALTHY</t>
+  </si>
+  <si>
+    <t>Only VERY_UNHEALTHY pollution rows shown</t>
+  </si>
+  <si>
+    <t>TC-F14-08</t>
+  </si>
+  <si>
+    <t>Filter by HAZARDOUS pollution level</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select HAZARDOUS. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;pollutionLevel=HAZARDOUS;expected_pollution=HAZARDOUS</t>
+  </si>
+  <si>
+    <t>Only HAZARDOUS pollution rows shown</t>
+  </si>
+  <si>
+    <t>TC-F14-09</t>
+  </si>
+  <si>
+    <t>TC-F14-10</t>
+  </si>
+  <si>
+    <t>TC-F14-11</t>
+  </si>
+  <si>
+    <t>Sort by CO high to low</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select CO high to low. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;sort=co:desc</t>
+  </si>
+  <si>
+    <t>Rows ordered CO descending</t>
+  </si>
+  <si>
+    <t>TC-F14-12</t>
+  </si>
+  <si>
+    <t>Sort by CO low to high</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select CO low to high. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;sort=co:asc</t>
+  </si>
+  <si>
+    <t>Rows ordered CO ascending</t>
+  </si>
+  <si>
+    <t>TC-F14-13</t>
+  </si>
+  <si>
+    <t>Sort by ozone high to low</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select ozone high to low. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;sort=ozone:desc</t>
+  </si>
+  <si>
+    <t>Rows ordered ozone descending</t>
+  </si>
+  <si>
+    <t>TC-F14-14</t>
+  </si>
+  <si>
+    <t>Sort by ozone low to high</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select ozone low to high. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;sort=ozone:asc</t>
+  </si>
+  <si>
+    <t>Rows ordered ozone ascending</t>
+  </si>
+  <si>
+    <t>TC-F14-15</t>
+  </si>
+  <si>
+    <t>Verifies actual sort order</t>
+  </si>
+  <si>
+    <t>TC-F14-16</t>
+  </si>
+  <si>
+    <t>TC-F14-17</t>
+  </si>
+  <si>
+    <t>TC-F14-18</t>
+  </si>
+  <si>
+    <t>TC-F14-19</t>
+  </si>
+  <si>
+    <t>TC-F14-20</t>
+  </si>
+  <si>
+    <t>TC-F14-21</t>
+  </si>
+  <si>
+    <t>TC-F14-22</t>
+  </si>
+  <si>
+    <t>TC-F14-23</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_NASR_CITY;pollutionLevel=HAZARDOUS</t>
+  </si>
+  <si>
+    <t>TC-F14-24</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_NASR_CITY</t>
+  </si>
+  <si>
+    <t>TC-F14-25</t>
+  </si>
+  <si>
+    <t>TC-F15-01</t>
+  </si>
+  <si>
+    <t>Alert banners appear after seeding air quality alerts</t>
+  </si>
+  <si>
+    <t>1. Seed AIR_POLLUTION alert via API. 2. Open dashboard</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;metric=co;threshold=1;condition=ABOVE;wait_ms=7000</t>
+  </si>
+  <si>
+    <t>TC-F15-02</t>
+  </si>
+  <si>
+    <t>TC-F15-03</t>
+  </si>
+  <si>
+    <t>TC-F15-04</t>
+  </si>
+  <si>
+    <t>TC-F15-05</t>
+  </si>
+  <si>
+    <t>1. Seed &gt;= 2 AIR_POLLUTION alerts. 2. Open dashboard quickly</t>
+  </si>
+  <si>
+    <t>TC-F13-14</t>
+  </si>
+  <si>
+    <t>1. Seed sensors. 2. Open /air-quality-dashboard. 3. Check analytics panel.</t>
+  </si>
+  <si>
+    <t>TC-F13-15</t>
+  </si>
+  <si>
+    <t>TC-F13-16</t>
+  </si>
+  <si>
+    <t>TC-F13-17</t>
+  </si>
+  <si>
+    <t>Street Light nav card is visible on /home</t>
+  </si>
+  <si>
+    <t>Street Light nav card is visible</t>
+  </si>
+  <si>
+    <t>Clicking street light card navigates to /street-light-dashboard</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Click street light nav card</t>
+  </si>
+  <si>
+    <t>URL contains /street-light-dashboard</t>
+  </si>
+  <si>
+    <t>/street-light-dashboard</t>
+  </si>
+  <si>
+    <t>Street Light card has correct title text</t>
+  </si>
+  <si>
+    <t>Card text contains street light or lighting keywords</t>
+  </si>
+  <si>
+    <t>Authenticated user opens /street-light-dashboard, page root visible</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Navigate to /street-light-dashboard</t>
+  </si>
+  <si>
+    <t>TC-F10-06</t>
+  </si>
+  <si>
+    <t>TC-F10-07</t>
+  </si>
+  <si>
+    <t>Street light readings table visible</t>
+  </si>
+  <si>
+    <t>TC-F10-08</t>
+  </si>
+  <si>
+    <t>Columns: Location, Timestamp, Brightness, Power, Status</t>
+  </si>
+  <si>
+    <t>TC-F10-09</t>
+  </si>
+  <si>
+    <t>TC-F10-10</t>
+  </si>
+  <si>
+    <t>TC-F10-11</t>
+  </si>
+  <si>
+    <t>TC-F10-12</t>
+  </si>
+  <si>
+    <t>1. Seed sensors. 2. Open /street-light-dashboard. 3. Read first row text.</t>
+  </si>
+  <si>
+    <t>First row text contains one of: CAIRO_ZAMALEK, CAIRO_DOWNTOWN, CAIRO_NEW_CAIRO</t>
+  </si>
+  <si>
+    <t>TC-F10-13</t>
+  </si>
+  <si>
+    <t>Unauthenticated user redirected to /login from /street-light-dashboard</t>
+  </si>
+  <si>
+    <t>1. No login. 2. Navigate to /street-light-dashboard</t>
+  </si>
+  <si>
+    <t>TC-F11-01</t>
+  </si>
+  <si>
+    <t>Filter by CAIRO_ZAMALEK location</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select Zamalek. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_ZAMALEK;expected_location=CAIRO_ZAMALEK</t>
+  </si>
+  <si>
+    <t>Only CAIRO_ZAMALEK rows shown</t>
+  </si>
+  <si>
+    <t>TC-F11-02</t>
+  </si>
+  <si>
+    <t>Filter by CAIRO_DOWNTOWN location</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select Downtown. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_DOWNTOWN;expected_location=CAIRO_DOWNTOWN</t>
+  </si>
+  <si>
+    <t>Only CAIRO_DOWNTOWN rows shown</t>
+  </si>
+  <si>
+    <t>TC-F11-03</t>
+  </si>
+  <si>
+    <t>Filter by CAIRO_NEW_CAIRO location</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select New Cairo. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_NEW_CAIRO;expected_location=CAIRO_NEW_CAIRO</t>
+  </si>
+  <si>
+    <t>Only CAIRO_NEW_CAIRO rows shown</t>
+  </si>
+  <si>
+    <t>TC-F11-04</t>
+  </si>
+  <si>
+    <t>Filter by ON status</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select ON. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;status=ON;expected_status=ON</t>
+  </si>
+  <si>
+    <t>Only ON status rows shown</t>
+  </si>
+  <si>
+    <t>TC-F11-05</t>
+  </si>
+  <si>
+    <t>Filter by OFF status</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select OFF. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;status=OFF;expected_status=OFF</t>
+  </si>
+  <si>
+    <t>Only OFF status rows shown</t>
+  </si>
+  <si>
+    <t>TC-F11-06</t>
+  </si>
+  <si>
+    <t>TC-F11-07</t>
+  </si>
+  <si>
+    <t>TC-F11-08</t>
+  </si>
+  <si>
+    <t>Sort by power consumption high to low</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select power high to low. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;sort=powerConsumption:desc</t>
+  </si>
+  <si>
+    <t>Rows ordered power consumption descending</t>
+  </si>
+  <si>
+    <t>TC-F11-09</t>
+  </si>
+  <si>
+    <t>Sort by power consumption low to high</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select power low to high. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;sort=powerConsumption:asc</t>
+  </si>
+  <si>
+    <t>Rows ordered power consumption ascending</t>
+  </si>
+  <si>
+    <t>TC-F11-10</t>
+  </si>
+  <si>
+    <t>Sort by brightness level low to high</t>
+  </si>
+  <si>
+    <t>1. Log in. 2. Open dashboard. 3. Select brightness low to high. 4. Apply</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;sort=brightnessLevel:asc</t>
+  </si>
+  <si>
+    <t>Rows ordered brightness ascending</t>
+  </si>
+  <si>
+    <t>TC-F11-11</t>
+  </si>
+  <si>
+    <t>TC-F11-12</t>
+  </si>
+  <si>
+    <t>TC-F11-13</t>
+  </si>
+  <si>
+    <t>TC-F11-14</t>
+  </si>
+  <si>
+    <t>TC-F11-15</t>
+  </si>
+  <si>
+    <t>TC-F11-16</t>
+  </si>
+  <si>
+    <t>TC-F11-17</t>
+  </si>
+  <si>
+    <t>TC-F11-18</t>
+  </si>
+  <si>
+    <t>TC-F11-19</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_ZAMALEK;status=OFF</t>
+  </si>
+  <si>
+    <t>TC-F11-20</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;location=CAIRO_ZAMALEK</t>
+  </si>
+  <si>
+    <t>TC-F11-21</t>
+  </si>
+  <si>
+    <t>TC-F12-01</t>
+  </si>
+  <si>
+    <t>Alert banners appear after seeding street light alerts</t>
+  </si>
+  <si>
+    <t>1. Seed STREET_LIGHT alert via API. 2. Open dashboard</t>
+  </si>
+  <si>
+    <t>email=john@example.com;password=Password123!;metric=powerConsumption;threshold=1;condition=ABOVE;wait_ms=7000</t>
+  </si>
+  <si>
+    <t>TC-F12-02</t>
+  </si>
+  <si>
+    <t>TC-F12-03</t>
+  </si>
+  <si>
+    <t>TC-F12-04</t>
+  </si>
+  <si>
+    <t>TC-F12-05</t>
+  </si>
+  <si>
+    <t>1. Seed &gt;= 2 STREET_LIGHT alerts. 2. Open dashboard quickly</t>
+  </si>
+  <si>
+    <t>TC-F10-14</t>
+  </si>
+  <si>
+    <t>1. Seed sensors. 2. Open /street-light-dashboard. 3. Check analytics panel.</t>
+  </si>
+  <si>
+    <t>TC-F10-15</t>
+  </si>
+  <si>
+    <t>TC-F10-16</t>
+  </si>
+  <si>
+    <t>TC-F10-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columns: Location Timestamp Density Avg Speed Congestion </t>
   </si>
 </sst>
 </file>
@@ -6762,7 +7395,7 @@
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="74" customWidth="1"/>
     <col min="9" max="9" width="109.6640625" customWidth="1"/>
-    <col min="10" max="10" width="56.6640625" customWidth="1"/>
+    <col min="10" max="10" width="65" customWidth="1"/>
     <col min="11" max="11" width="18.77734375" customWidth="1"/>
     <col min="12" max="12" width="15.109375" customWidth="1"/>
     <col min="13" max="13" width="16.6640625" customWidth="1"/>
@@ -6848,7 +7481,7 @@
         <v>830</v>
       </c>
       <c r="M2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -6886,7 +7519,7 @@
         <v>830</v>
       </c>
       <c r="M3" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -6924,7 +7557,7 @@
         <v>830</v>
       </c>
       <c r="M4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
@@ -6962,10 +7595,10 @@
         <v>830</v>
       </c>
       <c r="M5" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="N5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
@@ -7003,7 +7636,7 @@
         <v>830</v>
       </c>
       <c r="M6" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -7041,10 +7674,10 @@
         <v>830</v>
       </c>
       <c r="M7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="N7" t="s">
         <v>1044</v>
-      </c>
-      <c r="N7" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -7082,7 +7715,7 @@
         <v>830</v>
       </c>
       <c r="M8" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -7120,10 +7753,10 @@
         <v>830</v>
       </c>
       <c r="M9" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="N9" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -7155,13 +7788,13 @@
         <v>127</v>
       </c>
       <c r="J10" t="s">
-        <v>1021</v>
+        <v>1329</v>
       </c>
       <c r="L10" t="s">
         <v>830</v>
       </c>
       <c r="M10" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -7193,13 +7826,13 @@
         <v>127</v>
       </c>
       <c r="J11" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="L11" t="s">
         <v>830</v>
       </c>
       <c r="M11" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -7231,13 +7864,13 @@
         <v>127</v>
       </c>
       <c r="J12" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="L12" t="s">
         <v>830</v>
       </c>
       <c r="M12" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
@@ -7269,13 +7902,13 @@
         <v>127</v>
       </c>
       <c r="J13" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="L13" t="s">
         <v>830</v>
       </c>
       <c r="M13" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -7304,16 +7937,16 @@
         <v>986</v>
       </c>
       <c r="I14" s="89" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="J14" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="L14" t="s">
         <v>830</v>
       </c>
       <c r="M14" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -7342,16 +7975,16 @@
         <v>987</v>
       </c>
       <c r="I15" s="89" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="J15" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="L15" t="s">
         <v>830</v>
       </c>
       <c r="M15" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -7380,16 +8013,16 @@
         <v>988</v>
       </c>
       <c r="I16" s="89" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="J16" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="L16" t="s">
         <v>830</v>
       </c>
       <c r="M16" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
@@ -7418,16 +8051,16 @@
         <v>989</v>
       </c>
       <c r="I17" s="89" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="J17" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="L17" t="s">
         <v>830</v>
       </c>
       <c r="M17" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
@@ -7456,16 +8089,16 @@
         <v>990</v>
       </c>
       <c r="I18" s="89" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="J18" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="L18" t="s">
         <v>830</v>
       </c>
       <c r="M18" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
@@ -7494,16 +8127,16 @@
         <v>991</v>
       </c>
       <c r="I19" s="89" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="J19" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="L19" t="s">
         <v>830</v>
       </c>
       <c r="M19" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
@@ -7532,16 +8165,16 @@
         <v>992</v>
       </c>
       <c r="I20" s="89" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="J20" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="L20" t="s">
         <v>830</v>
       </c>
       <c r="M20" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
@@ -7570,16 +8203,16 @@
         <v>993</v>
       </c>
       <c r="I21" s="89" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="J21" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="L21" t="s">
         <v>830</v>
       </c>
       <c r="M21" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
@@ -7608,16 +8241,16 @@
         <v>994</v>
       </c>
       <c r="I22" s="89" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="J22" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="L22" t="s">
         <v>830</v>
       </c>
       <c r="M22" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
@@ -7646,16 +8279,16 @@
         <v>995</v>
       </c>
       <c r="I23" s="89" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="J23" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="L23" t="s">
         <v>830</v>
       </c>
       <c r="M23" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -7684,16 +8317,16 @@
         <v>996</v>
       </c>
       <c r="I24" s="89" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="J24" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="L24" t="s">
         <v>830</v>
       </c>
       <c r="M24" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
@@ -7722,16 +8355,16 @@
         <v>997</v>
       </c>
       <c r="I25" s="89" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="J25" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="L25" t="s">
         <v>830</v>
       </c>
       <c r="M25" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
@@ -7760,16 +8393,16 @@
         <v>998</v>
       </c>
       <c r="I26" s="89" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="J26" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="L26" t="s">
         <v>830</v>
       </c>
       <c r="M26" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
@@ -7801,13 +8434,13 @@
         <v>127</v>
       </c>
       <c r="J27" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="L27" t="s">
         <v>830</v>
       </c>
       <c r="M27" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
@@ -7839,13 +8472,13 @@
         <v>127</v>
       </c>
       <c r="J28" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="L28" t="s">
         <v>830</v>
       </c>
       <c r="M28" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -7877,13 +8510,13 @@
         <v>127</v>
       </c>
       <c r="J29" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="L29" t="s">
         <v>830</v>
       </c>
       <c r="M29" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -7915,13 +8548,13 @@
         <v>127</v>
       </c>
       <c r="J30" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="L30" t="s">
         <v>830</v>
       </c>
       <c r="M30" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
@@ -7950,16 +8583,16 @@
         <v>1003</v>
       </c>
       <c r="I31" s="89" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="J31" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="L31" t="s">
         <v>830</v>
       </c>
       <c r="M31" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
@@ -7988,16 +8621,16 @@
         <v>1004</v>
       </c>
       <c r="I32" s="89" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="J32" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="L32" t="s">
         <v>830</v>
       </c>
       <c r="M32" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.3">
@@ -8029,13 +8662,13 @@
         <v>127</v>
       </c>
       <c r="J33" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="L33" t="s">
         <v>830</v>
       </c>
       <c r="M33" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.3">
@@ -8064,19 +8697,19 @@
         <v>1006</v>
       </c>
       <c r="I34" s="89" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="J34" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="L34" t="s">
         <v>830</v>
       </c>
       <c r="M34" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="N34" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.3">
@@ -8105,16 +8738,16 @@
         <v>1007</v>
       </c>
       <c r="I35" s="89" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="J35" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="L35" t="s">
         <v>830</v>
       </c>
       <c r="M35" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.3">
@@ -8146,13 +8779,13 @@
         <v>127</v>
       </c>
       <c r="J36" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="L36" t="s">
         <v>830</v>
       </c>
       <c r="M36" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.3">
@@ -8181,19 +8814,19 @@
         <v>1009</v>
       </c>
       <c r="I37" s="89" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="J37" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="L37" t="s">
         <v>830</v>
       </c>
       <c r="M37" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="N37" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.3">
@@ -8222,16 +8855,16 @@
         <v>1010</v>
       </c>
       <c r="I38" s="89" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="J38" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="L38" t="s">
         <v>830</v>
       </c>
       <c r="M38" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.3">
@@ -8260,16 +8893,16 @@
         <v>1011</v>
       </c>
       <c r="I39" s="89" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="J39" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="L39" t="s">
         <v>830</v>
       </c>
       <c r="M39" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.3">
@@ -8298,16 +8931,16 @@
         <v>1012</v>
       </c>
       <c r="I40" s="89" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="J40" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="L40" t="s">
         <v>830</v>
       </c>
       <c r="M40" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.3">
@@ -8336,24 +8969,24 @@
         <v>1013</v>
       </c>
       <c r="I41" s="89" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="J41" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="L41" t="s">
         <v>830</v>
       </c>
       <c r="M41" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B42" t="s">
         <v>1059</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1060</v>
       </c>
       <c r="C42" t="s">
         <v>972</v>
@@ -8371,22 +9004,22 @@
         <v>62</v>
       </c>
       <c r="H42" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="I42" s="89" t="s">
         <v>127</v>
       </c>
       <c r="J42" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="K42" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="L42" t="s">
-        <v>1068</v>
+        <v>830</v>
       </c>
       <c r="M42" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="R42" s="89"/>
       <c r="S42" s="89"/>
@@ -8422,10 +9055,10 @@
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B43" t="s">
         <v>1061</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1062</v>
       </c>
       <c r="C43" t="s">
         <v>972</v>
@@ -8443,22 +9076,22 @@
         <v>62</v>
       </c>
       <c r="H43" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="I43" s="89" t="s">
         <v>127</v>
       </c>
       <c r="J43" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="K43" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="L43" t="s">
-        <v>1068</v>
+        <v>830</v>
       </c>
       <c r="M43" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="R43" s="89"/>
       <c r="S43" s="89"/>
@@ -8494,10 +9127,10 @@
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B44" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C44" t="s">
         <v>973</v>
@@ -8515,22 +9148,22 @@
         <v>49</v>
       </c>
       <c r="H44" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="I44" s="89" t="s">
         <v>127</v>
       </c>
       <c r="J44" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="L44" t="s">
         <v>830</v>
       </c>
       <c r="M44" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="N44" s="88" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="R44" s="89"/>
       <c r="S44" s="89"/>
@@ -8539,10 +9172,10 @@
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B45" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="C45" t="s">
         <v>974</v>
@@ -8560,22 +9193,22 @@
         <v>49</v>
       </c>
       <c r="H45" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I45" s="89" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J45" t="s">
         <v>1075</v>
-      </c>
-      <c r="I45" s="89" t="s">
-        <v>1085</v>
-      </c>
-      <c r="J45" t="s">
-        <v>1077</v>
       </c>
       <c r="L45" t="s">
         <v>830</v>
       </c>
       <c r="M45" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="N45" s="88" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="R45" s="89"/>
       <c r="S45" s="89"/>
@@ -8584,10 +9217,10 @@
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B46" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="C46" t="s">
         <v>975</v>
@@ -8605,27 +9238,27 @@
         <v>49</v>
       </c>
       <c r="H46" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="I46" t="s">
         <v>127</v>
       </c>
       <c r="J46" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="L46" t="s">
         <v>830</v>
       </c>
       <c r="M46" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="47" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B47" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="C47" t="s">
         <v>975</v>
@@ -8643,27 +9276,27 @@
         <v>49</v>
       </c>
       <c r="H47" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="I47" t="s">
         <v>127</v>
       </c>
       <c r="J47" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="L47" t="s">
         <v>830</v>
       </c>
       <c r="M47" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="48" spans="1:48" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B48" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="C48" t="s">
         <v>975</v>
@@ -8681,27 +9314,27 @@
         <v>49</v>
       </c>
       <c r="H48" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="I48" t="s">
         <v>127</v>
       </c>
       <c r="J48" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="L48" t="s">
         <v>830</v>
       </c>
       <c r="M48" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B49" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="C49" t="s">
         <v>975</v>
@@ -8719,27 +9352,27 @@
         <v>49</v>
       </c>
       <c r="H49" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="I49" t="s">
         <v>127</v>
       </c>
       <c r="J49" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="L49" t="s">
         <v>830</v>
       </c>
       <c r="M49" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="B50" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="C50" t="s">
         <v>975</v>
@@ -8751,25 +9384,25 @@
         <v>47</v>
       </c>
       <c r="F50" s="88" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G50" t="s">
         <v>49</v>
       </c>
       <c r="H50" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="I50" t="s">
         <v>127</v>
       </c>
       <c r="J50" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="L50" t="s">
         <v>830</v>
       </c>
       <c r="M50" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
   </sheetData>
@@ -8779,20 +9412,21 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66792E39-CB8E-4487-AB5C-D865B1B13B1B}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" customWidth="1"/>
+    <col min="2" max="2" width="63.44140625" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" customWidth="1"/>
     <col min="6" max="6" width="20.88671875" customWidth="1"/>
     <col min="7" max="7" width="15.21875" customWidth="1"/>
-    <col min="8" max="8" width="20.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="13" max="13" width="16.21875" customWidth="1"/>
+    <col min="8" max="8" width="82.21875" customWidth="1"/>
+    <col min="9" max="9" width="109.5546875" customWidth="1"/>
+    <col min="10" max="10" width="72.33203125" customWidth="1"/>
+    <col min="11" max="11" width="32.77734375" customWidth="1"/>
+    <col min="13" max="13" width="25.33203125" customWidth="1"/>
     <col min="14" max="14" width="49.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8838,6 +9472,1813 @@
       </c>
       <c r="N1" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C2" t="s">
+        <v>972</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" t="s">
+        <v>976</v>
+      </c>
+      <c r="I2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L2" t="s">
+        <v>830</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C3" t="s">
+        <v>972</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="I3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="L3" t="s">
+        <v>830</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C4" t="s">
+        <v>972</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>976</v>
+      </c>
+      <c r="I4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="L4" t="s">
+        <v>830</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B5" t="s">
+        <v>935</v>
+      </c>
+      <c r="C5" t="s">
+        <v>972</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" t="s">
+        <v>978</v>
+      </c>
+      <c r="I5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L5" t="s">
+        <v>830</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="N5" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C6" t="s">
+        <v>973</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1131</v>
+      </c>
+      <c r="I6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L6" t="s">
+        <v>830</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B7" t="s">
+        <v>938</v>
+      </c>
+      <c r="C7" t="s">
+        <v>973</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>981</v>
+      </c>
+      <c r="I7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L7" t="s">
+        <v>830</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B8" t="s">
+        <v>939</v>
+      </c>
+      <c r="C8" t="s">
+        <v>973</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>982</v>
+      </c>
+      <c r="I8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1134</v>
+      </c>
+      <c r="L8" t="s">
+        <v>830</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N8" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>940</v>
+      </c>
+      <c r="C9" t="s">
+        <v>973</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>214</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
+        <v>983</v>
+      </c>
+      <c r="I9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1136</v>
+      </c>
+      <c r="L9" t="s">
+        <v>830</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B10" t="s">
+        <v>941</v>
+      </c>
+      <c r="C10" t="s">
+        <v>973</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>214</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>984</v>
+      </c>
+      <c r="I10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L10" t="s">
+        <v>830</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B11" t="s">
+        <v>942</v>
+      </c>
+      <c r="C11" t="s">
+        <v>973</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" t="s">
+        <v>985</v>
+      </c>
+      <c r="I11" t="s">
+        <v>127</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1022</v>
+      </c>
+      <c r="L11" t="s">
+        <v>830</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B12" t="s">
+        <v>943</v>
+      </c>
+      <c r="C12" t="s">
+        <v>973</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
+        <v>214</v>
+      </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" t="s">
+        <v>984</v>
+      </c>
+      <c r="I12" t="s">
+        <v>127</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L12" t="s">
+        <v>830</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C13" t="s">
+        <v>973</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" t="s">
+        <v>214</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I13" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1142</v>
+      </c>
+      <c r="L13" t="s">
+        <v>830</v>
+      </c>
+      <c r="M13" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N13" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C14" t="s">
+        <v>973</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" t="s">
+        <v>214</v>
+      </c>
+      <c r="G14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I14" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L14" t="s">
+        <v>830</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N14" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C15" t="s">
+        <v>974</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" t="s">
+        <v>214</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1149</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1150</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1151</v>
+      </c>
+      <c r="L15" t="s">
+        <v>830</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C16" t="s">
+        <v>974</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1155</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1156</v>
+      </c>
+      <c r="L16" t="s">
+        <v>830</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C17" t="s">
+        <v>974</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>214</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="L17" t="s">
+        <v>830</v>
+      </c>
+      <c r="M17" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C18" t="s">
+        <v>974</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>214</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1166</v>
+      </c>
+      <c r="L18" t="s">
+        <v>830</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C19" t="s">
+        <v>974</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>214</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" t="s">
+        <v>990</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1169</v>
+      </c>
+      <c r="J19" t="s">
+        <v>1170</v>
+      </c>
+      <c r="L19" t="s">
+        <v>830</v>
+      </c>
+      <c r="M19" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C20" t="s">
+        <v>974</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" t="s">
+        <v>214</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I20" t="s">
+        <v>1174</v>
+      </c>
+      <c r="J20" t="s">
+        <v>1175</v>
+      </c>
+      <c r="L20" t="s">
+        <v>830</v>
+      </c>
+      <c r="M20" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C21" t="s">
+        <v>974</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
+        <v>214</v>
+      </c>
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J21" t="s">
+        <v>1180</v>
+      </c>
+      <c r="L21" t="s">
+        <v>830</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C22" t="s">
+        <v>974</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" t="s">
+        <v>214</v>
+      </c>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1183</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1184</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1185</v>
+      </c>
+      <c r="L22" t="s">
+        <v>830</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B23" t="s">
+        <v>951</v>
+      </c>
+      <c r="C23" t="s">
+        <v>974</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" t="s">
+        <v>214</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" t="s">
+        <v>993</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J23" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L23" t="s">
+        <v>830</v>
+      </c>
+      <c r="M23" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B24" t="s">
+        <v>952</v>
+      </c>
+      <c r="C24" t="s">
+        <v>974</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" t="s">
+        <v>214</v>
+      </c>
+      <c r="G24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" t="s">
+        <v>994</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J24" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L24" t="s">
+        <v>830</v>
+      </c>
+      <c r="M24" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C25" t="s">
+        <v>974</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" t="s">
+        <v>214</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1190</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1191</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1192</v>
+      </c>
+      <c r="L25" t="s">
+        <v>830</v>
+      </c>
+      <c r="M25" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C26" t="s">
+        <v>974</v>
+      </c>
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" t="s">
+        <v>214</v>
+      </c>
+      <c r="G26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1196</v>
+      </c>
+      <c r="J26" t="s">
+        <v>1197</v>
+      </c>
+      <c r="L26" t="s">
+        <v>830</v>
+      </c>
+      <c r="M26" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C27" t="s">
+        <v>974</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" t="s">
+        <v>214</v>
+      </c>
+      <c r="G27" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1200</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1201</v>
+      </c>
+      <c r="J27" t="s">
+        <v>1202</v>
+      </c>
+      <c r="L27" t="s">
+        <v>830</v>
+      </c>
+      <c r="M27" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C28" t="s">
+        <v>974</v>
+      </c>
+      <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" t="s">
+        <v>214</v>
+      </c>
+      <c r="G28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1205</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J28" t="s">
+        <v>1207</v>
+      </c>
+      <c r="L28" t="s">
+        <v>830</v>
+      </c>
+      <c r="M28" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C29" t="s">
+        <v>974</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" t="s">
+        <v>214</v>
+      </c>
+      <c r="G29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1075</v>
+      </c>
+      <c r="L29" t="s">
+        <v>830</v>
+      </c>
+      <c r="M29" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N29" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B30" t="s">
+        <v>957</v>
+      </c>
+      <c r="C30" t="s">
+        <v>974</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" t="s">
+        <v>214</v>
+      </c>
+      <c r="G30" t="s">
+        <v>49</v>
+      </c>
+      <c r="H30" t="s">
+        <v>999</v>
+      </c>
+      <c r="I30" t="s">
+        <v>127</v>
+      </c>
+      <c r="J30" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L30" t="s">
+        <v>830</v>
+      </c>
+      <c r="M30" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B31" t="s">
+        <v>958</v>
+      </c>
+      <c r="C31" t="s">
+        <v>974</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" t="s">
+        <v>214</v>
+      </c>
+      <c r="G31" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I31" t="s">
+        <v>127</v>
+      </c>
+      <c r="J31" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L31" t="s">
+        <v>830</v>
+      </c>
+      <c r="M31" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B32" t="s">
+        <v>959</v>
+      </c>
+      <c r="C32" t="s">
+        <v>974</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" t="s">
+        <v>214</v>
+      </c>
+      <c r="G32" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I32" t="s">
+        <v>127</v>
+      </c>
+      <c r="J32" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L32" t="s">
+        <v>830</v>
+      </c>
+      <c r="M32" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B33" t="s">
+        <v>960</v>
+      </c>
+      <c r="C33" t="s">
+        <v>974</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" t="s">
+        <v>214</v>
+      </c>
+      <c r="G33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I33" t="s">
+        <v>127</v>
+      </c>
+      <c r="J33" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L33" t="s">
+        <v>830</v>
+      </c>
+      <c r="M33" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B34" t="s">
+        <v>961</v>
+      </c>
+      <c r="C34" t="s">
+        <v>974</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" t="s">
+        <v>214</v>
+      </c>
+      <c r="G34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1089</v>
+      </c>
+      <c r="J34" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L34" t="s">
+        <v>830</v>
+      </c>
+      <c r="M34" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B35" t="s">
+        <v>962</v>
+      </c>
+      <c r="C35" t="s">
+        <v>974</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" t="s">
+        <v>214</v>
+      </c>
+      <c r="G35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L35" t="s">
+        <v>830</v>
+      </c>
+      <c r="M35" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B36" t="s">
+        <v>963</v>
+      </c>
+      <c r="C36" t="s">
+        <v>974</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" t="s">
+        <v>214</v>
+      </c>
+      <c r="G36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I36" t="s">
+        <v>127</v>
+      </c>
+      <c r="J36" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L36" t="s">
+        <v>830</v>
+      </c>
+      <c r="M36" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B37" t="s">
+        <v>964</v>
+      </c>
+      <c r="C37" t="s">
+        <v>974</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" t="s">
+        <v>214</v>
+      </c>
+      <c r="G37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1218</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1048</v>
+      </c>
+      <c r="L37" t="s">
+        <v>830</v>
+      </c>
+      <c r="M37" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N37" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B38" t="s">
+        <v>965</v>
+      </c>
+      <c r="C38" t="s">
+        <v>974</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" t="s">
+        <v>214</v>
+      </c>
+      <c r="G38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1220</v>
+      </c>
+      <c r="J38" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L38" t="s">
+        <v>830</v>
+      </c>
+      <c r="M38" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B39" t="s">
+        <v>966</v>
+      </c>
+      <c r="C39" t="s">
+        <v>974</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" t="s">
+        <v>47</v>
+      </c>
+      <c r="F39" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I39" t="s">
+        <v>127</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L39" t="s">
+        <v>830</v>
+      </c>
+      <c r="M39" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C40" t="s">
+        <v>975</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F40" t="s">
+        <v>214</v>
+      </c>
+      <c r="G40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L40" t="s">
+        <v>830</v>
+      </c>
+      <c r="M40" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N40" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B41" t="s">
+        <v>968</v>
+      </c>
+      <c r="C41" t="s">
+        <v>975</v>
+      </c>
+      <c r="D41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41" t="s">
+        <v>214</v>
+      </c>
+      <c r="G41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J41" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L41" t="s">
+        <v>830</v>
+      </c>
+      <c r="M41" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B42" t="s">
+        <v>969</v>
+      </c>
+      <c r="C42" t="s">
+        <v>975</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" t="s">
+        <v>214</v>
+      </c>
+      <c r="G42" t="s">
+        <v>49</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I42" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J42" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L42" t="s">
+        <v>830</v>
+      </c>
+      <c r="M42" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B43" t="s">
+        <v>970</v>
+      </c>
+      <c r="C43" t="s">
+        <v>975</v>
+      </c>
+      <c r="D43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43" t="s">
+        <v>214</v>
+      </c>
+      <c r="G43" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J43" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L43" t="s">
+        <v>830</v>
+      </c>
+      <c r="M43" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B44" t="s">
+        <v>971</v>
+      </c>
+      <c r="C44" t="s">
+        <v>975</v>
+      </c>
+      <c r="D44" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" t="s">
+        <v>47</v>
+      </c>
+      <c r="F44" t="s">
+        <v>214</v>
+      </c>
+      <c r="G44" t="s">
+        <v>49</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J44" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L44" t="s">
+        <v>830</v>
+      </c>
+      <c r="M44" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C45" t="s">
+        <v>975</v>
+      </c>
+      <c r="D45" t="s">
+        <v>46</v>
+      </c>
+      <c r="E45" t="s">
+        <v>47</v>
+      </c>
+      <c r="F45" t="s">
+        <v>214</v>
+      </c>
+      <c r="G45" t="s">
+        <v>49</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1232</v>
+      </c>
+      <c r="I45" t="s">
+        <v>127</v>
+      </c>
+      <c r="J45" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L45" t="s">
+        <v>830</v>
+      </c>
+      <c r="M45" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C46" t="s">
+        <v>975</v>
+      </c>
+      <c r="D46" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" t="s">
+        <v>47</v>
+      </c>
+      <c r="F46" t="s">
+        <v>214</v>
+      </c>
+      <c r="G46" t="s">
+        <v>49</v>
+      </c>
+      <c r="H46" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I46" t="s">
+        <v>127</v>
+      </c>
+      <c r="J46" t="s">
+        <v>1110</v>
+      </c>
+      <c r="L46" t="s">
+        <v>830</v>
+      </c>
+      <c r="M46" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C47" t="s">
+        <v>975</v>
+      </c>
+      <c r="D47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" t="s">
+        <v>47</v>
+      </c>
+      <c r="F47" t="s">
+        <v>214</v>
+      </c>
+      <c r="G47" t="s">
+        <v>49</v>
+      </c>
+      <c r="H47" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I47" t="s">
+        <v>127</v>
+      </c>
+      <c r="J47" t="s">
+        <v>1111</v>
+      </c>
+      <c r="L47" t="s">
+        <v>830</v>
+      </c>
+      <c r="M47" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C48" t="s">
+        <v>975</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" t="s">
+        <v>214</v>
+      </c>
+      <c r="G48" t="s">
+        <v>49</v>
+      </c>
+      <c r="H48" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I48" t="s">
+        <v>127</v>
+      </c>
+      <c r="J48" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L48" t="s">
+        <v>830</v>
+      </c>
+      <c r="M48" t="s">
+        <v>1124</v>
       </c>
     </row>
   </sheetData>
@@ -8847,20 +11288,21 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8F9AE2C-88B6-407A-BDBC-8F35AAEBF418}">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="65.88671875" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" customWidth="1"/>
     <col min="5" max="5" width="22.5546875" customWidth="1"/>
     <col min="6" max="6" width="20.88671875" customWidth="1"/>
     <col min="7" max="7" width="15.21875" customWidth="1"/>
-    <col min="8" max="8" width="20.88671875" customWidth="1"/>
-    <col min="9" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="8" max="8" width="68.5546875" customWidth="1"/>
+    <col min="9" max="9" width="108.44140625" customWidth="1"/>
+    <col min="10" max="10" width="78.21875" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="13" max="13" width="16.21875" customWidth="1"/>
+    <col min="13" max="13" width="24.109375" customWidth="1"/>
     <col min="14" max="14" width="49.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8906,6 +11348,1661 @@
       </c>
       <c r="N1" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C2" t="s">
+        <v>972</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" t="s">
+        <v>976</v>
+      </c>
+      <c r="I2" t="s">
+        <v>127</v>
+      </c>
+      <c r="J2" t="s">
+        <v>1237</v>
+      </c>
+      <c r="L2" t="s">
+        <v>830</v>
+      </c>
+      <c r="M2" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C3" t="s">
+        <v>972</v>
+      </c>
+      <c r="D3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" t="s">
+        <v>214</v>
+      </c>
+      <c r="G3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="I3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="L3" t="s">
+        <v>830</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C4" t="s">
+        <v>972</v>
+      </c>
+      <c r="D4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" t="s">
+        <v>214</v>
+      </c>
+      <c r="G4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" t="s">
+        <v>976</v>
+      </c>
+      <c r="I4" t="s">
+        <v>127</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L4" t="s">
+        <v>830</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>935</v>
+      </c>
+      <c r="C5" t="s">
+        <v>972</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H5" t="s">
+        <v>978</v>
+      </c>
+      <c r="I5" t="s">
+        <v>127</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L5" t="s">
+        <v>830</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="N5" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C6" t="s">
+        <v>973</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1245</v>
+      </c>
+      <c r="I6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L6" t="s">
+        <v>830</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B7" t="s">
+        <v>938</v>
+      </c>
+      <c r="C7" t="s">
+        <v>973</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="s">
+        <v>981</v>
+      </c>
+      <c r="I7" t="s">
+        <v>127</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="L7" t="s">
+        <v>830</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B8" t="s">
+        <v>939</v>
+      </c>
+      <c r="C8" t="s">
+        <v>973</v>
+      </c>
+      <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>214</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>982</v>
+      </c>
+      <c r="I8" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="L8" t="s">
+        <v>830</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1241</v>
+      </c>
+      <c r="N8" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B9" t="s">
+        <v>940</v>
+      </c>
+      <c r="C9" t="s">
+        <v>973</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" t="s">
+        <v>214</v>
+      </c>
+      <c r="G9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" t="s">
+        <v>983</v>
+      </c>
+      <c r="I9" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1250</v>
+      </c>
+      <c r="L9" t="s">
+        <v>830</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B10" t="s">
+        <v>941</v>
+      </c>
+      <c r="C10" t="s">
+        <v>973</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>214</v>
+      </c>
+      <c r="G10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" t="s">
+        <v>984</v>
+      </c>
+      <c r="I10" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L10" t="s">
+        <v>830</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B11" t="s">
+        <v>942</v>
+      </c>
+      <c r="C11" t="s">
+        <v>973</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
+        <v>214</v>
+      </c>
+      <c r="G11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" t="s">
+        <v>985</v>
+      </c>
+      <c r="I11" t="s">
+        <v>127</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1022</v>
+      </c>
+      <c r="L11" t="s">
+        <v>830</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B12" t="s">
+        <v>943</v>
+      </c>
+      <c r="C12" t="s">
+        <v>973</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
+        <v>214</v>
+      </c>
+      <c r="G12" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" t="s">
+        <v>984</v>
+      </c>
+      <c r="I12" t="s">
+        <v>127</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="L12" t="s">
+        <v>830</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C13" t="s">
+        <v>973</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" t="s">
+        <v>214</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1255</v>
+      </c>
+      <c r="I13" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1256</v>
+      </c>
+      <c r="L13" t="s">
+        <v>830</v>
+      </c>
+      <c r="M13" t="s">
+        <v>1241</v>
+      </c>
+      <c r="N13" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C14" t="s">
+        <v>973</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" t="s">
+        <v>214</v>
+      </c>
+      <c r="G14" t="s">
+        <v>62</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1259</v>
+      </c>
+      <c r="I14" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1017</v>
+      </c>
+      <c r="L14" t="s">
+        <v>830</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1241</v>
+      </c>
+      <c r="N14" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C15" t="s">
+        <v>974</v>
+      </c>
+      <c r="D15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" t="s">
+        <v>214</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1262</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1263</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1264</v>
+      </c>
+      <c r="L15" t="s">
+        <v>830</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C16" t="s">
+        <v>974</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1267</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1268</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1269</v>
+      </c>
+      <c r="L16" t="s">
+        <v>830</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C17" t="s">
+        <v>974</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" t="s">
+        <v>214</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1272</v>
+      </c>
+      <c r="I17" t="s">
+        <v>1273</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1274</v>
+      </c>
+      <c r="L17" t="s">
+        <v>830</v>
+      </c>
+      <c r="M17" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C18" t="s">
+        <v>974</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" t="s">
+        <v>214</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1278</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1279</v>
+      </c>
+      <c r="L18" t="s">
+        <v>830</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C19" t="s">
+        <v>974</v>
+      </c>
+      <c r="D19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" t="s">
+        <v>214</v>
+      </c>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1282</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J19" t="s">
+        <v>1284</v>
+      </c>
+      <c r="L19" t="s">
+        <v>830</v>
+      </c>
+      <c r="M19" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B20" t="s">
+        <v>951</v>
+      </c>
+      <c r="C20" t="s">
+        <v>974</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" t="s">
+        <v>214</v>
+      </c>
+      <c r="G20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" t="s">
+        <v>993</v>
+      </c>
+      <c r="I20" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L20" t="s">
+        <v>830</v>
+      </c>
+      <c r="M20" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B21" t="s">
+        <v>952</v>
+      </c>
+      <c r="C21" t="s">
+        <v>974</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" t="s">
+        <v>214</v>
+      </c>
+      <c r="G21" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" t="s">
+        <v>994</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J21" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L21" t="s">
+        <v>830</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C22" t="s">
+        <v>974</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" t="s">
+        <v>214</v>
+      </c>
+      <c r="G22" t="s">
+        <v>49</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1289</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1291</v>
+      </c>
+      <c r="L22" t="s">
+        <v>830</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C23" t="s">
+        <v>974</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" t="s">
+        <v>214</v>
+      </c>
+      <c r="G23" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1294</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1295</v>
+      </c>
+      <c r="J23" t="s">
+        <v>1296</v>
+      </c>
+      <c r="L23" t="s">
+        <v>830</v>
+      </c>
+      <c r="M23" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C24" t="s">
+        <v>974</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" t="s">
+        <v>214</v>
+      </c>
+      <c r="G24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1299</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J24" t="s">
+        <v>1301</v>
+      </c>
+      <c r="L24" t="s">
+        <v>830</v>
+      </c>
+      <c r="M24" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C25" t="s">
+        <v>974</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" t="s">
+        <v>214</v>
+      </c>
+      <c r="G25" t="s">
+        <v>49</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1083</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1075</v>
+      </c>
+      <c r="L25" t="s">
+        <v>830</v>
+      </c>
+      <c r="M25" t="s">
+        <v>1241</v>
+      </c>
+      <c r="N25" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B26" t="s">
+        <v>957</v>
+      </c>
+      <c r="C26" t="s">
+        <v>974</v>
+      </c>
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" t="s">
+        <v>214</v>
+      </c>
+      <c r="G26" t="s">
+        <v>49</v>
+      </c>
+      <c r="H26" t="s">
+        <v>999</v>
+      </c>
+      <c r="I26" t="s">
+        <v>127</v>
+      </c>
+      <c r="J26" t="s">
+        <v>1037</v>
+      </c>
+      <c r="L26" t="s">
+        <v>830</v>
+      </c>
+      <c r="M26" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B27" t="s">
+        <v>958</v>
+      </c>
+      <c r="C27" t="s">
+        <v>974</v>
+      </c>
+      <c r="D27" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" t="s">
+        <v>214</v>
+      </c>
+      <c r="G27" t="s">
+        <v>49</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1000</v>
+      </c>
+      <c r="I27" t="s">
+        <v>127</v>
+      </c>
+      <c r="J27" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L27" t="s">
+        <v>830</v>
+      </c>
+      <c r="M27" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B28" t="s">
+        <v>959</v>
+      </c>
+      <c r="C28" t="s">
+        <v>974</v>
+      </c>
+      <c r="D28" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" t="s">
+        <v>214</v>
+      </c>
+      <c r="G28" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I28" t="s">
+        <v>127</v>
+      </c>
+      <c r="J28" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L28" t="s">
+        <v>830</v>
+      </c>
+      <c r="M28" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B29" t="s">
+        <v>960</v>
+      </c>
+      <c r="C29" t="s">
+        <v>974</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F29" t="s">
+        <v>214</v>
+      </c>
+      <c r="G29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1002</v>
+      </c>
+      <c r="I29" t="s">
+        <v>127</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1040</v>
+      </c>
+      <c r="L29" t="s">
+        <v>830</v>
+      </c>
+      <c r="M29" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B30" t="s">
+        <v>961</v>
+      </c>
+      <c r="C30" t="s">
+        <v>974</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30" t="s">
+        <v>214</v>
+      </c>
+      <c r="G30" t="s">
+        <v>49</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1003</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1089</v>
+      </c>
+      <c r="J30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L30" t="s">
+        <v>830</v>
+      </c>
+      <c r="M30" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B31" t="s">
+        <v>962</v>
+      </c>
+      <c r="C31" t="s">
+        <v>974</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" t="s">
+        <v>214</v>
+      </c>
+      <c r="G31" t="s">
+        <v>49</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J31" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L31" t="s">
+        <v>830</v>
+      </c>
+      <c r="M31" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B32" t="s">
+        <v>963</v>
+      </c>
+      <c r="C32" t="s">
+        <v>974</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" t="s">
+        <v>214</v>
+      </c>
+      <c r="G32" t="s">
+        <v>49</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I32" t="s">
+        <v>127</v>
+      </c>
+      <c r="J32" t="s">
+        <v>1047</v>
+      </c>
+      <c r="L32" t="s">
+        <v>830</v>
+      </c>
+      <c r="M32" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B33" t="s">
+        <v>964</v>
+      </c>
+      <c r="C33" t="s">
+        <v>974</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" t="s">
+        <v>214</v>
+      </c>
+      <c r="G33" t="s">
+        <v>62</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1006</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J33" t="s">
+        <v>1048</v>
+      </c>
+      <c r="L33" t="s">
+        <v>830</v>
+      </c>
+      <c r="M33" t="s">
+        <v>1241</v>
+      </c>
+      <c r="N33" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B34" t="s">
+        <v>965</v>
+      </c>
+      <c r="C34" t="s">
+        <v>974</v>
+      </c>
+      <c r="D34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" t="s">
+        <v>214</v>
+      </c>
+      <c r="G34" t="s">
+        <v>49</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J34" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L34" t="s">
+        <v>830</v>
+      </c>
+      <c r="M34" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B35" t="s">
+        <v>966</v>
+      </c>
+      <c r="C35" t="s">
+        <v>974</v>
+      </c>
+      <c r="D35" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" t="s">
+        <v>214</v>
+      </c>
+      <c r="G35" t="s">
+        <v>49</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I35" t="s">
+        <v>127</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1050</v>
+      </c>
+      <c r="L35" t="s">
+        <v>830</v>
+      </c>
+      <c r="M35" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C36" t="s">
+        <v>975</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" t="s">
+        <v>214</v>
+      </c>
+      <c r="G36" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I36" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J36" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L36" t="s">
+        <v>830</v>
+      </c>
+      <c r="M36" t="s">
+        <v>1241</v>
+      </c>
+      <c r="N36" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B37" t="s">
+        <v>968</v>
+      </c>
+      <c r="C37" t="s">
+        <v>975</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" t="s">
+        <v>47</v>
+      </c>
+      <c r="F37" t="s">
+        <v>214</v>
+      </c>
+      <c r="G37" t="s">
+        <v>49</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1052</v>
+      </c>
+      <c r="L37" t="s">
+        <v>830</v>
+      </c>
+      <c r="M37" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B38" t="s">
+        <v>969</v>
+      </c>
+      <c r="C38" t="s">
+        <v>975</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" t="s">
+        <v>47</v>
+      </c>
+      <c r="F38" t="s">
+        <v>214</v>
+      </c>
+      <c r="G38" t="s">
+        <v>49</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J38" t="s">
+        <v>1053</v>
+      </c>
+      <c r="L38" t="s">
+        <v>830</v>
+      </c>
+      <c r="M38" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B39" t="s">
+        <v>970</v>
+      </c>
+      <c r="C39" t="s">
+        <v>975</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" t="s">
+        <v>47</v>
+      </c>
+      <c r="F39" t="s">
+        <v>214</v>
+      </c>
+      <c r="G39" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L39" t="s">
+        <v>830</v>
+      </c>
+      <c r="M39" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B40" t="s">
+        <v>971</v>
+      </c>
+      <c r="C40" t="s">
+        <v>975</v>
+      </c>
+      <c r="D40" t="s">
+        <v>46</v>
+      </c>
+      <c r="E40" t="s">
+        <v>47</v>
+      </c>
+      <c r="F40" t="s">
+        <v>214</v>
+      </c>
+      <c r="G40" t="s">
+        <v>49</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1055</v>
+      </c>
+      <c r="L40" t="s">
+        <v>830</v>
+      </c>
+      <c r="M40" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C41" t="s">
+        <v>975</v>
+      </c>
+      <c r="D41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" t="s">
+        <v>47</v>
+      </c>
+      <c r="F41" t="s">
+        <v>214</v>
+      </c>
+      <c r="G41" t="s">
+        <v>49</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I41" t="s">
+        <v>127</v>
+      </c>
+      <c r="J41" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L41" t="s">
+        <v>830</v>
+      </c>
+      <c r="M41" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C42" t="s">
+        <v>975</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" t="s">
+        <v>47</v>
+      </c>
+      <c r="F42" t="s">
+        <v>214</v>
+      </c>
+      <c r="G42" t="s">
+        <v>49</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1105</v>
+      </c>
+      <c r="I42" t="s">
+        <v>127</v>
+      </c>
+      <c r="J42" t="s">
+        <v>1110</v>
+      </c>
+      <c r="L42" t="s">
+        <v>830</v>
+      </c>
+      <c r="M42" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C43" t="s">
+        <v>975</v>
+      </c>
+      <c r="D43" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" t="s">
+        <v>47</v>
+      </c>
+      <c r="F43" t="s">
+        <v>214</v>
+      </c>
+      <c r="G43" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1106</v>
+      </c>
+      <c r="I43" t="s">
+        <v>127</v>
+      </c>
+      <c r="J43" t="s">
+        <v>1111</v>
+      </c>
+      <c r="L43" t="s">
+        <v>830</v>
+      </c>
+      <c r="M43" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C44" t="s">
+        <v>975</v>
+      </c>
+      <c r="D44" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" t="s">
+        <v>47</v>
+      </c>
+      <c r="F44" t="s">
+        <v>214</v>
+      </c>
+      <c r="G44" t="s">
+        <v>49</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I44" t="s">
+        <v>127</v>
+      </c>
+      <c r="J44" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L44" t="s">
+        <v>830</v>
+      </c>
+      <c r="M44" t="s">
+        <v>1241</v>
       </c>
     </row>
   </sheetData>
@@ -23502,6 +27599,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="11" max="11" width="100.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -24152,6 +28252,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="8" max="8" width="25.88671875" customWidth="1"/>
+    <col min="9" max="9" width="57.33203125" customWidth="1"/>
+    <col min="10" max="10" width="81.109375" customWidth="1"/>
+    <col min="11" max="11" width="116.5546875" customWidth="1"/>
+    <col min="12" max="12" width="46.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
